--- a/InputFiles/GC/TC01_GC_phs003519_SmpTumSta-Tumor_SampleType_Analyte_ExpStr-RNASeq.xlsx
+++ b/InputFiles/GC/TC01_GC_phs003519_SmpTumSta-Tumor_SampleType_Analyte_ExpStr-RNASeq.xlsx
@@ -539,6 +539,7 @@
         <is>
           <t xml:space="preserve">MATCH (samp:sample)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
 MATCH (f:file)-[:of_participant]-&gt;(p)
+MATCH (f)-[:from_sample]-&gt;(samp)
 WHERE s.phs_accession = "phs003519"
   AND samp.sample_tumor_status = "Tumor"
   AND samp.sample_type = "Analyte"
